--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-22T13:28:22.777Z</t>
+    <t>2026-10-06T13:48:11.974Z</t>
   </si>
   <si>
     <t>Home | Parker US</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="117">
   <si>
     <t>_reportFile</t>
   </si>
@@ -19,6 +19,12 @@
     <t>blocks</t>
   </si>
   <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>errorStack</t>
+  </si>
+  <si>
     <t>path</t>
   </si>
   <si>
@@ -43,6 +49,9 @@
     <t>["hero-banner","columns-media","columns-media","carousel-hero","banner-cta","cards-category","cards-news"]</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>us/en/home</t>
   </si>
   <si>
@@ -52,13 +61,309 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-10-06T13:48:11.974Z</t>
+    <t>2026-10-07T05:56:50.782Z</t>
   </si>
   <si>
     <t>Home | Parker US</t>
   </si>
   <si>
     <t>https://www.parker.com/us/en/home.html</t>
+  </si>
+  <si>
+    <t>us/en/markets.report.json</t>
+  </si>
+  <si>
+    <t>["carousel-hero","columns-media","columns-media","cards-teaser","cards-teaser","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>us/en/markets</t>
+  </si>
+  <si>
+    <t>markets-2</t>
+  </si>
+  <si>
+    <t>2026-10-07T05:25:07.351Z</t>
+  </si>
+  <si>
+    <t>Trends &amp; Markets | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/aerospace-and-defense.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","columns-media","columns-media","columns-media","columns-media","cards-teaser","banner-inline","hero-card","cards-news","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/aerospace-and-defense</t>
+  </si>
+  <si>
+    <t>markets</t>
+  </si>
+  <si>
+    <t>2026-10-07T05:56:49.969Z</t>
+  </si>
+  <si>
+    <t>Aerospace &amp; Defense | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/aerospace-and-defense.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/aerospace-industry-trends.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","columns-media","cards-teaser","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/aerospace-industry-trends</t>
+  </si>
+  <si>
+    <t>2026-10-07T03:36:00.411Z</t>
+  </si>
+  <si>
+    <t>Aerospace and Defense Trends | Parker Innovation in AI, Green Aviation &amp; Manufacturing | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/aerospace-industry-trends.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/clean-tech-trends.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","columns-media","columns-media","cards-teaser","cards-teaser","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/clean-tech-trends</t>
+  </si>
+  <si>
+    <t>2026-10-07T03:36:54.212Z</t>
+  </si>
+  <si>
+    <t>Clean Tech Trends in Manufacturing | Energy, AI &amp; Sustainability Insights | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/clean-tech-trends.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/digitalization-trends.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","columns-media","columns-media","cards-teaser","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/digitalization-trends</t>
+  </si>
+  <si>
+    <t>2026-10-07T03:37:47.847Z</t>
+  </si>
+  <si>
+    <t>Digitalization Trends in Manufacturing | IoT, Innovation &amp; Industry Insights | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/digitalization-trends.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/electrification-trends.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","columns-media","columns-media","columns-media","cards-teaser","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/electrification-trends</t>
+  </si>
+  <si>
+    <t>2026-10-07T03:38:40.307Z</t>
+  </si>
+  <si>
+    <t>Electrification Trends | Parker Insights on Technology, Markets &amp; Sustainability | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/electrification-trends.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/electronics-and-semiconductors.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","cards-teaser","hero-card","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/electronics-and-semiconductors</t>
+  </si>
+  <si>
+    <t>2026-10-07T05:18:26.659Z</t>
+  </si>
+  <si>
+    <t>Electronics &amp; Semiconductors | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/electronics-and-semiconductors.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/energy.report.json</t>
+  </si>
+  <si>
+    <t>us/en/markets/energy</t>
+  </si>
+  <si>
+    <t>2026-10-07T05:12:41.004Z</t>
+  </si>
+  <si>
+    <t>Energy | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/energy.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/hvac-and-refrigeration.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","columns-media","cards-teaser","banner-inline","cards-news","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/hvac-and-refrigeration</t>
+  </si>
+  <si>
+    <t>2026-10-07T05:12:43.843Z</t>
+  </si>
+  <si>
+    <t>HVAC &amp; Refrigeration | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/hvac-and-refrigeration.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/in-plant-and-industrial-equipment.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","columns-media","cards-teaser","banner-inline","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/in-plant-and-industrial-equipment</t>
+  </si>
+  <si>
+    <t>2026-10-07T03:41:24.517Z</t>
+  </si>
+  <si>
+    <t>In-Plant &amp; Industrial Equipment | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/in-plant-and-industrial-equipment.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/interactive-library.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","cards-teaser","cards-teaser","cards-teaser","cards-teaser","cards-teaser","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/interactive-library</t>
+  </si>
+  <si>
+    <t>2026-10-07T05:13:36.314Z</t>
+  </si>
+  <si>
+    <t>Interactive Library | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/interactive-library.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/life-sciences.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","columns-media","columns-media","columns-media","cards-teaser","hero-card","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/life-sciences</t>
+  </si>
+  <si>
+    <t>2026-10-07T03:43:10.517Z</t>
+  </si>
+  <si>
+    <t>Life Sciences | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/life-sciences.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/off-highway.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","columns-media","columns-media","columns-media","columns-media","cards-teaser","banner-inline","hero-card","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/off-highway</t>
+  </si>
+  <si>
+    <t>2026-10-07T03:44:02.903Z</t>
+  </si>
+  <si>
+    <t>Off-Highway | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/off-highway.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/transportation.html.report.json</t>
+  </si>
+  <si>
+    <t>page.goto: Target page, context or browser has been closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page.goto: Target page, context or browser has been closed
+    at processUrl (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:599:20)
+    at async main (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:956:22)</t>
+  </si>
+  <si>
+    <t>us/en/markets/transportation.html</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>2026-10-07T03:24:38.088Z</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/transportation.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/transportation.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","columns-media","cards-teaser","cards-news","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/transportation</t>
+  </si>
+  <si>
+    <t>2026-10-07T05:14:30.302Z</t>
+  </si>
+  <si>
+    <t>Transportation | Parker US</t>
+  </si>
+  <si>
+    <t>us/en/markets/interactive-library/parker-world.report.json</t>
+  </si>
+  <si>
+    <t>["embed-app","banner-cta","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/interactive-library/parker-world</t>
+  </si>
+  <si>
+    <t>interactive-library</t>
+  </si>
+  <si>
+    <t>2026-10-07T05:50:08.421Z</t>
+  </si>
+  <si>
+    <t>Parker World | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/interactive-library/parker-world.html</t>
   </si>
 </sst>
 </file>
@@ -447,19 +752,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="1" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="49" customWidth="1"/>
+    <col min="7" max="7" width="21" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="10" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -484,35 +787,559 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" t="s">
+        <v>71</v>
+      </c>
+      <c r="I11" t="s">
+        <v>72</v>
+      </c>
+      <c r="J11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" t="s">
+        <v>77</v>
+      </c>
+      <c r="I12" t="s">
+        <v>78</v>
+      </c>
+      <c r="J12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" t="s">
+        <v>83</v>
+      </c>
+      <c r="I13" t="s">
+        <v>84</v>
+      </c>
+      <c r="J13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" t="s">
+        <v>89</v>
+      </c>
+      <c r="I14" t="s">
+        <v>90</v>
+      </c>
+      <c r="J14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" t="s">
+        <v>95</v>
+      </c>
+      <c r="I15" t="s">
+        <v>96</v>
+      </c>
+      <c r="J15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" t="s">
+        <v>102</v>
+      </c>
+      <c r="G16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" t="s">
+        <v>103</v>
+      </c>
+      <c r="I16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
+        <v>107</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" t="s">
+        <v>108</v>
+      </c>
+      <c r="I17" t="s">
+        <v>109</v>
+      </c>
+      <c r="J17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s">
+        <v>113</v>
+      </c>
+      <c r="H18" t="s">
+        <v>114</v>
+      </c>
+      <c r="I18" t="s">
+        <v>115</v>
+      </c>
+      <c r="J18" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="309">
   <si>
     <t>_reportFile</t>
   </si>
@@ -43,25 +43,46 @@
     <t>url</t>
   </si>
   <si>
+    <t>us/en/category.report.json</t>
+  </si>
+  <si>
+    <t>["columns-media","cards-category","cards-category","cards-category","cards-category","cards-category","cards-category","cards-category","cards-category","cards-category","cards-category","cards-category","cards-category","cards-category","cards-category","cards-category","cards-category","cards-category","cards-category","cards-category"]</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>us/en/category</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>product-landing</t>
+  </si>
+  <si>
+    <t>2026-10-08T03:21:27.567Z</t>
+  </si>
+  <si>
+    <t>Products | Parker US</t>
+  </si>
+  <si>
+    <t>https://ph.parker.com/us/en/category</t>
+  </si>
+  <si>
     <t>us/en/home.report.json</t>
   </si>
   <si>
     <t>["hero-banner","columns-media","columns-media","carousel-hero","banner-cta","cards-category","cards-news"]</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>us/en/home</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>home</t>
   </si>
   <si>
-    <t>2026-10-07T05:56:50.782Z</t>
+    <t>2026-10-08T04:11:15.879Z</t>
   </si>
   <si>
     <t>Home | Parker US</t>
@@ -82,7 +103,7 @@
     <t>markets-2</t>
   </si>
   <si>
-    <t>2026-10-07T05:25:07.351Z</t>
+    <t>2026-10-07T05:56:56.851Z</t>
   </si>
   <si>
     <t>Trends &amp; Markets | Parker US</t>
@@ -91,223 +112,123 @@
     <t>https://www.parker.com/us/en/markets.html</t>
   </si>
   <si>
-    <t>us/en/markets/aerospace-and-defense.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","columns-media","columns-media","columns-media","columns-media","columns-media","cards-teaser","banner-inline","hero-card","cards-news","banner-cta"]</t>
-  </si>
-  <si>
-    <t>us/en/markets/aerospace-and-defense</t>
-  </si>
-  <si>
-    <t>markets</t>
-  </si>
-  <si>
-    <t>2026-10-07T05:56:49.969Z</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense | Parker US</t>
-  </si>
-  <si>
-    <t>https://www.parker.com/us/en/markets/aerospace-and-defense.html</t>
-  </si>
-  <si>
-    <t>us/en/markets/aerospace-industry-trends.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","columns-media","columns-media","cards-teaser","banner-cta"]</t>
-  </si>
-  <si>
-    <t>us/en/markets/aerospace-industry-trends</t>
-  </si>
-  <si>
-    <t>2026-10-07T03:36:00.411Z</t>
-  </si>
-  <si>
-    <t>Aerospace and Defense Trends | Parker Innovation in AI, Green Aviation &amp; Manufacturing | Parker US</t>
-  </si>
-  <si>
-    <t>https://www.parker.com/us/en/markets/aerospace-industry-trends.html</t>
-  </si>
-  <si>
-    <t>us/en/markets/clean-tech-trends.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","columns-media","columns-media","columns-media","cards-teaser","cards-teaser","banner-cta"]</t>
-  </si>
-  <si>
-    <t>us/en/markets/clean-tech-trends</t>
-  </si>
-  <si>
-    <t>2026-10-07T03:36:54.212Z</t>
-  </si>
-  <si>
-    <t>Clean Tech Trends in Manufacturing | Energy, AI &amp; Sustainability Insights | Parker US</t>
-  </si>
-  <si>
-    <t>https://www.parker.com/us/en/markets/clean-tech-trends.html</t>
-  </si>
-  <si>
-    <t>us/en/markets/digitalization-trends.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","columns-media","columns-media","columns-media","cards-teaser","banner-cta"]</t>
-  </si>
-  <si>
-    <t>us/en/markets/digitalization-trends</t>
-  </si>
-  <si>
-    <t>2026-10-07T03:37:47.847Z</t>
-  </si>
-  <si>
-    <t>Digitalization Trends in Manufacturing | IoT, Innovation &amp; Industry Insights | Parker US</t>
-  </si>
-  <si>
-    <t>https://www.parker.com/us/en/markets/digitalization-trends.html</t>
-  </si>
-  <si>
-    <t>us/en/markets/electrification-trends.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","columns-media","columns-media","columns-media","columns-media","cards-teaser","banner-cta"]</t>
-  </si>
-  <si>
-    <t>us/en/markets/electrification-trends</t>
-  </si>
-  <si>
-    <t>2026-10-07T03:38:40.307Z</t>
-  </si>
-  <si>
-    <t>Electrification Trends | Parker Insights on Technology, Markets &amp; Sustainability | Parker US</t>
-  </si>
-  <si>
-    <t>https://www.parker.com/us/en/markets/electrification-trends.html</t>
-  </si>
-  <si>
-    <t>us/en/markets/electronics-and-semiconductors.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","columns-media","cards-teaser","hero-card","banner-cta"]</t>
-  </si>
-  <si>
-    <t>us/en/markets/electronics-and-semiconductors</t>
-  </si>
-  <si>
-    <t>2026-10-07T05:18:26.659Z</t>
-  </si>
-  <si>
-    <t>Electronics &amp; Semiconductors | Parker US</t>
-  </si>
-  <si>
-    <t>https://www.parker.com/us/en/markets/electronics-and-semiconductors.html</t>
-  </si>
-  <si>
-    <t>us/en/markets/energy.report.json</t>
-  </si>
-  <si>
-    <t>us/en/markets/energy</t>
-  </si>
-  <si>
-    <t>2026-10-07T05:12:41.004Z</t>
-  </si>
-  <si>
-    <t>Energy | Parker US</t>
-  </si>
-  <si>
-    <t>https://www.parker.com/us/en/markets/energy.html</t>
-  </si>
-  <si>
-    <t>us/en/markets/hvac-and-refrigeration.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","columns-media","columns-media","cards-teaser","banner-inline","cards-news","banner-cta"]</t>
-  </si>
-  <si>
-    <t>us/en/markets/hvac-and-refrigeration</t>
-  </si>
-  <si>
-    <t>2026-10-07T05:12:43.843Z</t>
-  </si>
-  <si>
-    <t>HVAC &amp; Refrigeration | Parker US</t>
-  </si>
-  <si>
-    <t>https://www.parker.com/us/en/markets/hvac-and-refrigeration.html</t>
-  </si>
-  <si>
-    <t>us/en/markets/in-plant-and-industrial-equipment.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","columns-media","columns-media","cards-teaser","banner-inline","banner-cta"]</t>
-  </si>
-  <si>
-    <t>us/en/markets/in-plant-and-industrial-equipment</t>
-  </si>
-  <si>
-    <t>2026-10-07T03:41:24.517Z</t>
-  </si>
-  <si>
-    <t>In-Plant &amp; Industrial Equipment | Parker US</t>
-  </si>
-  <si>
-    <t>https://www.parker.com/us/en/markets/in-plant-and-industrial-equipment.html</t>
-  </si>
-  <si>
-    <t>us/en/markets/interactive-library.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","columns-media","cards-teaser","cards-teaser","cards-teaser","cards-teaser","cards-teaser","cards-teaser"]</t>
-  </si>
-  <si>
-    <t>us/en/markets/interactive-library</t>
-  </si>
-  <si>
-    <t>2026-10-07T05:13:36.314Z</t>
-  </si>
-  <si>
-    <t>Interactive Library | Parker US</t>
-  </si>
-  <si>
-    <t>https://www.parker.com/us/en/markets/interactive-library.html</t>
-  </si>
-  <si>
-    <t>us/en/markets/life-sciences.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","columns-media","columns-media","columns-media","columns-media","cards-teaser","hero-card","banner-cta"]</t>
-  </si>
-  <si>
-    <t>us/en/markets/life-sciences</t>
-  </si>
-  <si>
-    <t>2026-10-07T03:43:10.517Z</t>
-  </si>
-  <si>
-    <t>Life Sciences | Parker US</t>
-  </si>
-  <si>
-    <t>https://www.parker.com/us/en/markets/life-sciences.html</t>
-  </si>
-  <si>
-    <t>us/en/markets/off-highway.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","columns-media","columns-media","columns-media","columns-media","columns-media","cards-teaser","banner-inline","hero-card","banner-cta"]</t>
-  </si>
-  <si>
-    <t>us/en/markets/off-highway</t>
-  </si>
-  <si>
-    <t>2026-10-07T03:44:02.903Z</t>
-  </si>
-  <si>
-    <t>Off-Highway | Parker US</t>
-  </si>
-  <si>
-    <t>https://www.parker.com/us/en/markets/off-highway.html</t>
-  </si>
-  <si>
-    <t>us/en/markets/transportation.html.report.json</t>
+    <t>us/en/support.report.json</t>
+  </si>
+  <si>
+    <t>["cards-teaser","cards-teaser","cards-contact","cards-news"]</t>
+  </si>
+  <si>
+    <t>us/en/support</t>
+  </si>
+  <si>
+    <t>support-landing</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:58:03.168Z</t>
+  </si>
+  <si>
+    <t>Help &amp; Support | Parker US</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support</t>
+  </si>
+  <si>
+    <t>us/en/category/adhesives-coatings-and-encapsulants.report.json</t>
+  </si>
+  <si>
+    <t>BLOCKED_PAGE: ACCESS_DENIED — "access denied"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error: BLOCKED_PAGE: ACCESS_DENIED — "access denied"
+    at processUrl (file:///home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:631:15)
+    at async main (file:///home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:1014:33)</t>
+  </si>
+  <si>
+    <t>us/en/category/adhesives-coatings-and-encapsulants</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>2026-10-08T03:03:14.355Z</t>
+  </si>
+  <si>
+    <t>https://ph.parker.com/us/en/category/adhesives-coatings-and-encapsulants</t>
+  </si>
+  <si>
+    <t>us/en/category/aerospace-systems-and-technologies.report.json</t>
+  </si>
+  <si>
+    <t>us/en/category/aerospace-systems-and-technologies</t>
+  </si>
+  <si>
+    <t>2026-10-08T03:04:18.512Z</t>
+  </si>
+  <si>
+    <t>https://ph.parker.com/us/en/category/aerospace-systems-and-technologies</t>
+  </si>
+  <si>
+    <t>us/en/category/air-preparation-frl-and-dryers.report.json</t>
+  </si>
+  <si>
+    <t>us/en/category/air-preparation-frl-and-dryers</t>
+  </si>
+  <si>
+    <t>2026-10-08T03:05:14.585Z</t>
+  </si>
+  <si>
+    <t>https://ph.parker.com/us/en/category/air-preparation-frl-and-dryers</t>
+  </si>
+  <si>
+    <t>us/en/category/bioprocessing-and-medical-technologies.report.json</t>
+  </si>
+  <si>
+    <t>us/en/category/bioprocessing-and-medical-technologies</t>
+  </si>
+  <si>
+    <t>2026-10-08T03:06:09.868Z</t>
+  </si>
+  <si>
+    <t>https://ph.parker.com/us/en/category/bioprocessing-and-medical-technologies</t>
+  </si>
+  <si>
+    <t>us/en/category/cylinders-and-actuators.report.json</t>
+  </si>
+  <si>
+    <t>us/en/category/cylinders-and-actuators</t>
+  </si>
+  <si>
+    <t>2026-10-08T03:07:08.278Z</t>
+  </si>
+  <si>
+    <t>https://ph.parker.com/us/en/category/cylinders-and-actuators</t>
+  </si>
+  <si>
+    <t>us/en/category/emi-shielding.report.json</t>
+  </si>
+  <si>
+    <t>us/en/category/emi-shielding</t>
+  </si>
+  <si>
+    <t>2026-10-08T03:08:02.437Z</t>
+  </si>
+  <si>
+    <t>https://ph.parker.com/us/en/category/emi-shielding</t>
+  </si>
+  <si>
+    <t>us/en/category/filters-collectors-separators-purifiers.report.json</t>
+  </si>
+  <si>
+    <t>us/en/category/filters-collectors-separators-purifiers</t>
+  </si>
+  <si>
+    <t>2026-10-08T03:08:58.055Z</t>
+  </si>
+  <si>
+    <t>https://ph.parker.com/us/en/category/filters-collectors-separators-purifiers</t>
+  </si>
+  <si>
+    <t>us/en/category/fittings-and-quick-couplings.report.json</t>
   </si>
   <si>
     <t>page.goto: Target page, context or browser has been closed</t>
@@ -318,12 +239,258 @@
     at async main (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:956:22)</t>
   </si>
   <si>
+    <t>us/en/category/fittings-and-quick-couplings</t>
+  </si>
+  <si>
+    <t>2026-10-08T03:09:13.503Z</t>
+  </si>
+  <si>
+    <t>https://ph.parker.com/us/en/category/fittings-and-quick-couplings</t>
+  </si>
+  <si>
+    <t>us/en/category/hose-piping-and-tubing.report.json</t>
+  </si>
+  <si>
+    <t>["columns-media","cards-category"]</t>
+  </si>
+  <si>
+    <t>us/en/category/hose-piping-and-tubing</t>
+  </si>
+  <si>
+    <t>product-category</t>
+  </si>
+  <si>
+    <t>2026-10-08T03:21:33.079Z</t>
+  </si>
+  <si>
+    <t>Hose, Piping and Tubing | Parker US</t>
+  </si>
+  <si>
+    <t>https://ph.parker.com/us/en/category/hose-piping-and-tubing</t>
+  </si>
+  <si>
+    <t>us/en/markets/aerospace-and-defense.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","columns-media","columns-media","columns-media","columns-media","cards-teaser","banner-inline","hero-card","cards-news","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/aerospace-and-defense</t>
+  </si>
+  <si>
+    <t>markets</t>
+  </si>
+  <si>
+    <t>2026-10-07T05:56:49.969Z</t>
+  </si>
+  <si>
+    <t>Aerospace &amp; Defense | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/aerospace-and-defense.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/aerospace-industry-trends.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","columns-media","cards-teaser","cards-teaser","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/aerospace-industry-trends</t>
+  </si>
+  <si>
+    <t>2026-10-07T05:57:44.211Z</t>
+  </si>
+  <si>
+    <t>Aerospace and Defense Trends | Parker Innovation in AI, Green Aviation &amp; Manufacturing | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/aerospace-industry-trends.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/clean-tech-trends.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","columns-media","columns-media","cards-teaser","cards-teaser","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/clean-tech-trends</t>
+  </si>
+  <si>
+    <t>2026-10-07T05:58:36.318Z</t>
+  </si>
+  <si>
+    <t>Clean Tech Trends in Manufacturing | Energy, AI &amp; Sustainability Insights | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/clean-tech-trends.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/digitalization-trends.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","columns-media","columns-media","cards-teaser","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/digitalization-trends</t>
+  </si>
+  <si>
+    <t>2026-10-07T05:59:29.809Z</t>
+  </si>
+  <si>
+    <t>Digitalization Trends in Manufacturing | IoT, Innovation &amp; Industry Insights | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/digitalization-trends.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/electrification-trends.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","columns-media","columns-media","columns-media","cards-teaser","cards-teaser","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/electrification-trends</t>
+  </si>
+  <si>
+    <t>2026-10-07T06:00:23.635Z</t>
+  </si>
+  <si>
+    <t>Electrification Trends | Parker Insights on Technology, Markets &amp; Sustainability | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/electrification-trends.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/electronics-and-semiconductors.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","cards-teaser","hero-card","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/electronics-and-semiconductors</t>
+  </si>
+  <si>
+    <t>2026-10-07T06:01:15.626Z</t>
+  </si>
+  <si>
+    <t>Electronics &amp; Semiconductors | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/electronics-and-semiconductors.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/energy.report.json</t>
+  </si>
+  <si>
+    <t>us/en/markets/energy</t>
+  </si>
+  <si>
+    <t>2026-10-07T06:01:18.858Z</t>
+  </si>
+  <si>
+    <t>Energy | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/energy.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/hvac-and-refrigeration.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","columns-media","cards-teaser","banner-inline","cards-news","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/hvac-and-refrigeration</t>
+  </si>
+  <si>
+    <t>2026-10-07T06:01:21.241Z</t>
+  </si>
+  <si>
+    <t>HVAC &amp; Refrigeration | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/hvac-and-refrigeration.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/in-plant-and-industrial-equipment.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","columns-media","cards-teaser","banner-inline","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/in-plant-and-industrial-equipment</t>
+  </si>
+  <si>
+    <t>2026-10-07T06:02:13.064Z</t>
+  </si>
+  <si>
+    <t>In-Plant &amp; Industrial Equipment | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/in-plant-and-industrial-equipment.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/interactive-library.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","cards-teaser","cards-teaser","cards-teaser","cards-teaser","cards-teaser","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/interactive-library</t>
+  </si>
+  <si>
+    <t>2026-10-07T06:03:06.144Z</t>
+  </si>
+  <si>
+    <t>Interactive Library | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/interactive-library.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/life-sciences.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","columns-media","columns-media","columns-media","cards-teaser","hero-card","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/life-sciences</t>
+  </si>
+  <si>
+    <t>2026-10-07T06:03:58.874Z</t>
+  </si>
+  <si>
+    <t>Life Sciences | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/life-sciences.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/off-highway.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-media","columns-media","columns-media","columns-media","columns-media","cards-teaser","banner-inline","hero-card","banner-cta"]</t>
+  </si>
+  <si>
+    <t>us/en/markets/off-highway</t>
+  </si>
+  <si>
+    <t>2026-10-07T06:04:51.007Z</t>
+  </si>
+  <si>
+    <t>Off-Highway | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/markets/off-highway.html</t>
+  </si>
+  <si>
+    <t>us/en/markets/transportation.html.report.json</t>
+  </si>
+  <si>
     <t>us/en/markets/transportation.html</t>
   </si>
   <si>
-    <t>failed</t>
-  </si>
-  <si>
     <t>2026-10-07T03:24:38.088Z</t>
   </si>
   <si>
@@ -339,12 +506,354 @@
     <t>us/en/markets/transportation</t>
   </si>
   <si>
-    <t>2026-10-07T05:14:30.302Z</t>
+    <t>2026-10-07T06:05:43.916Z</t>
   </si>
   <si>
     <t>Transportation | Parker US</t>
   </si>
   <si>
+    <t>us/en/support/billing-shipping.report.json</t>
+  </si>
+  <si>
+    <t>["cards-teaser"]</t>
+  </si>
+  <si>
+    <t>us/en/support/billing-shipping</t>
+  </si>
+  <si>
+    <t>support-topic</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:19:17.256Z</t>
+  </si>
+  <si>
+    <t>Billing &amp; Shipping - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/billing-shipping</t>
+  </si>
+  <si>
+    <t>us/en/support/cad-files.report.json</t>
+  </si>
+  <si>
+    <t>us/en/support/cad-files</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:20:11.521Z</t>
+  </si>
+  <si>
+    <t>CAD Files - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/cad-files</t>
+  </si>
+  <si>
+    <t>us/en/support/catalog-part-manuals.report.json</t>
+  </si>
+  <si>
+    <t>us/en/support/catalog-part-manuals</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:21:06.185Z</t>
+  </si>
+  <si>
+    <t>Catalogs and Part Manuals - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/catalog-part-manuals</t>
+  </si>
+  <si>
+    <t>us/en/support/cbc-report.report.json</t>
+  </si>
+  <si>
+    <t>us/en/support/cbc-report</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:21:58.146Z</t>
+  </si>
+  <si>
+    <t>CbC Report - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/cbc-report</t>
+  </si>
+  <si>
+    <t>us/en/support/certificates-compliance.report.json</t>
+  </si>
+  <si>
+    <t>us/en/support/certificates-compliance</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:22:51.099Z</t>
+  </si>
+  <si>
+    <t>Certificates and Compliance - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/certificates-compliance</t>
+  </si>
+  <si>
+    <t>us/en/support/contact-information.report.json</t>
+  </si>
+  <si>
+    <t>us/en/support/contact-information</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:23:44.901Z</t>
+  </si>
+  <si>
+    <t>Contact Information - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/contact-information</t>
+  </si>
+  <si>
+    <t>us/en/support/cross-reference.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>us/en/support/cross-reference</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:24:37.425Z</t>
+  </si>
+  <si>
+    <t>Cross Reference - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/cross-reference</t>
+  </si>
+  <si>
+    <t>us/en/support/ethics-integrity.report.json</t>
+  </si>
+  <si>
+    <t>us/en/support/ethics-integrity</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:25:32.867Z</t>
+  </si>
+  <si>
+    <t>Ethics Integrity - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/ethics-integrity</t>
+  </si>
+  <si>
+    <t>us/en/support/general-help.report.json</t>
+  </si>
+  <si>
+    <t>["columns-contact"]</t>
+  </si>
+  <si>
+    <t>us/en/support/general-help</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:27:19.917Z</t>
+  </si>
+  <si>
+    <t>General Help - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/general-help</t>
+  </si>
+  <si>
+    <t>us/en/support/hr-benefits.report.json</t>
+  </si>
+  <si>
+    <t>["cards-contact"]</t>
+  </si>
+  <si>
+    <t>us/en/support/hr-benefits</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:28:12.632Z</t>
+  </si>
+  <si>
+    <t>Human Resources &amp; Benefits - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/hr-benefits</t>
+  </si>
+  <si>
+    <t>us/en/support/installation-maintenance.report.json</t>
+  </si>
+  <si>
+    <t>["cards-teaser","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>us/en/support/installation-maintenance</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:29:06.349Z</t>
+  </si>
+  <si>
+    <t>Installation, Troubleshooting, Maintenance - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/installation-maintenance</t>
+  </si>
+  <si>
+    <t>us/en/support/investors.report.json</t>
+  </si>
+  <si>
+    <t>us/en/support/investors</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:30:00.931Z</t>
+  </si>
+  <si>
+    <t>Investor Questions - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/investors</t>
+  </si>
+  <si>
+    <t>us/en/support/optimization.report.json</t>
+  </si>
+  <si>
+    <t>us/en/support/optimization</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:30:53.017Z</t>
+  </si>
+  <si>
+    <t>Optimization - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/optimization</t>
+  </si>
+  <si>
+    <t>us/en/support/order-status.report.json</t>
+  </si>
+  <si>
+    <t>["cards-teaser","columns-media"]</t>
+  </si>
+  <si>
+    <t>us/en/support/order-status</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:30:54.986Z</t>
+  </si>
+  <si>
+    <t>Order Status - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/order-status</t>
+  </si>
+  <si>
+    <t>us/en/support/place-an-order.report.json</t>
+  </si>
+  <si>
+    <t>us/en/support/place-an-order</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:33:35.143Z</t>
+  </si>
+  <si>
+    <t>Place an Order - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/place-an-order</t>
+  </si>
+  <si>
+    <t>us/en/support/price-quote.report.json</t>
+  </si>
+  <si>
+    <t>us/en/support/price-quote</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:34:29.206Z</t>
+  </si>
+  <si>
+    <t>Price Quote and Availability - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/price-quote</t>
+  </si>
+  <si>
+    <t>us/en/support/repairs.report.json</t>
+  </si>
+  <si>
+    <t>us/en/support/repairs</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:35:22.190Z</t>
+  </si>
+  <si>
+    <t>Repairs - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/repairs</t>
+  </si>
+  <si>
+    <t>us/en/support/replacement.report.json</t>
+  </si>
+  <si>
+    <t>us/en/support/replacement</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:36:15.902Z</t>
+  </si>
+  <si>
+    <t>Replacement - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/replacement</t>
+  </si>
+  <si>
+    <t>us/en/support/software.report.json</t>
+  </si>
+  <si>
+    <t>us/en/support/software</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:37:09.573Z</t>
+  </si>
+  <si>
+    <t>Software - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/software</t>
+  </si>
+  <si>
+    <t>us/en/support/training-tutorials.report.json</t>
+  </si>
+  <si>
+    <t>us/en/support/training-tutorials</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:38:01.984Z</t>
+  </si>
+  <si>
+    <t>Training &amp; Tutorials - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/training-tutorials</t>
+  </si>
+  <si>
+    <t>us/en/industries/digital/pts.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","carousel-media","carousel-media","columns-media","columns-media","columns-media","cards-teaser","cards-teaser","cards-teaser","cards-video"]</t>
+  </si>
+  <si>
+    <t>us/en/industries/digital/pts</t>
+  </si>
+  <si>
+    <t>pts</t>
+  </si>
+  <si>
+    <t>2026-10-08T04:11:11.428Z</t>
+  </si>
+  <si>
+    <t>Asset Management | Parker US</t>
+  </si>
+  <si>
+    <t>https://www.parker.com/us/en/industries/digital/pts.html</t>
+  </si>
+  <si>
     <t>us/en/markets/interactive-library/parker-world.report.json</t>
   </si>
   <si>
@@ -357,13 +866,82 @@
     <t>interactive-library</t>
   </si>
   <si>
-    <t>2026-10-07T05:50:08.421Z</t>
+    <t>2026-10-07T05:57:01.467Z</t>
   </si>
   <si>
     <t>Parker World | Parker US</t>
   </si>
   <si>
     <t>https://www.parker.com/us/en/markets/interactive-library/parker-world.html</t>
+  </si>
+  <si>
+    <t>us/en/support/find-a-part/18605.report.json</t>
+  </si>
+  <si>
+    <t>["cards-news"]</t>
+  </si>
+  <si>
+    <t>us/en/support/find-a-part/18605</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:26:27.052Z</t>
+  </si>
+  <si>
+    <t>Find a Part - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/find-a-part/18605</t>
+  </si>
+  <si>
+    <t>us/en/support/master-directory/global-offices.report.json</t>
+  </si>
+  <si>
+    <t>["embed-app"]</t>
+  </si>
+  <si>
+    <t>us/en/support/master-directory/global-offices</t>
+  </si>
+  <si>
+    <t>master-directory</t>
+  </si>
+  <si>
+    <t>2026-10-07T17:04:52.843Z</t>
+  </si>
+  <si>
+    <t>Global Sales Offices - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/master-directory/global-offices</t>
+  </si>
+  <si>
+    <t>us/en/support/part-configuration/configurator-help.report.json</t>
+  </si>
+  <si>
+    <t>us/en/support/part-configuration/configurator-help</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:31:47.336Z</t>
+  </si>
+  <si>
+    <t>Part Configuration - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/part-configuration/configurator-help</t>
+  </si>
+  <si>
+    <t>us/en/support/part-information/18605.report.json</t>
+  </si>
+  <si>
+    <t>us/en/support/part-information/18605</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:32:39.743Z</t>
+  </si>
+  <si>
+    <t>Part Information - Help &amp; Support</t>
+  </si>
+  <si>
+    <t>https://help.parker.com/us/en/support/part-information/18605</t>
   </si>
 </sst>
 </file>
@@ -752,11 +1330,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="49" customWidth="1"/>
+    <col min="1" max="5" width="50" customWidth="1"/>
     <col min="7" max="7" width="21" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
     <col min="9" max="10" width="50" customWidth="1"/>
@@ -910,77 +1487,77 @@
         <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I6" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="J6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I7" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="J7" t="s">
         <v>50</v>
@@ -991,199 +1568,199 @@
         <v>51</v>
       </c>
       <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
         <v>52</v>
       </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" t="s">
         <v>53</v>
       </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" t="s">
         <v>54</v>
-      </c>
-      <c r="I8" t="s">
-        <v>55</v>
-      </c>
-      <c r="J8" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" t="s">
         <v>57</v>
       </c>
-      <c r="B9" t="s">
+      <c r="I9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" t="s">
         <v>58</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J9" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H10" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I10" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="J10" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H11" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="I11" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="J11" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E12" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="G12" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H12" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I12" t="s">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="J12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="G13" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H13" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="I13" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="J13" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
@@ -1192,30 +1769,30 @@
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I14" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
@@ -1224,62 +1801,62 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="J15" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F16" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="I16" t="s">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="J16" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
@@ -1288,54 +1865,1206 @@
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F17" t="s">
         <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I17" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="J17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" t="s">
+        <v>106</v>
+      </c>
+      <c r="I18" t="s">
+        <v>107</v>
+      </c>
+      <c r="J18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" t="s">
         <v>110</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
         <v>111</v>
       </c>
-      <c r="C18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" t="s">
         <v>112</v>
       </c>
-      <c r="F18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="I19" t="s">
         <v>113</v>
       </c>
-      <c r="H18" t="s">
+      <c r="J19" t="s">
         <v>114</v>
       </c>
-      <c r="I18" t="s">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>115</v>
       </c>
-      <c r="J18" t="s">
+      <c r="B20" t="s">
         <v>116</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s">
+        <v>87</v>
+      </c>
+      <c r="H20" t="s">
+        <v>118</v>
+      </c>
+      <c r="I20" t="s">
+        <v>119</v>
+      </c>
+      <c r="J20" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" t="s">
+        <v>122</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>87</v>
+      </c>
+      <c r="H21" t="s">
+        <v>123</v>
+      </c>
+      <c r="I21" t="s">
+        <v>124</v>
+      </c>
+      <c r="J21" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" t="s">
+        <v>87</v>
+      </c>
+      <c r="H22" t="s">
+        <v>129</v>
+      </c>
+      <c r="I22" t="s">
+        <v>130</v>
+      </c>
+      <c r="J22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" t="s">
+        <v>133</v>
+      </c>
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>134</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s">
+        <v>87</v>
+      </c>
+      <c r="H23" t="s">
+        <v>135</v>
+      </c>
+      <c r="I23" t="s">
+        <v>136</v>
+      </c>
+      <c r="J23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" t="s">
+        <v>140</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24" t="s">
+        <v>141</v>
+      </c>
+      <c r="I24" t="s">
+        <v>142</v>
+      </c>
+      <c r="J24" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>144</v>
+      </c>
+      <c r="B25" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
+        <v>146</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s">
+        <v>87</v>
+      </c>
+      <c r="H25" t="s">
+        <v>147</v>
+      </c>
+      <c r="I25" t="s">
+        <v>148</v>
+      </c>
+      <c r="J25" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>150</v>
+      </c>
+      <c r="B26" t="s">
+        <v>151</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" t="s">
+        <v>152</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" t="s">
+        <v>87</v>
+      </c>
+      <c r="H26" t="s">
+        <v>153</v>
+      </c>
+      <c r="I26" t="s">
+        <v>154</v>
+      </c>
+      <c r="J26" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>156</v>
+      </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" t="s">
+        <v>157</v>
+      </c>
+      <c r="F27" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" t="s">
+        <v>158</v>
+      </c>
+      <c r="I27" t="s">
+        <v>12</v>
+      </c>
+      <c r="J27" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>160</v>
+      </c>
+      <c r="B28" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" t="s">
+        <v>87</v>
+      </c>
+      <c r="H28" t="s">
+        <v>163</v>
+      </c>
+      <c r="I28" t="s">
+        <v>164</v>
+      </c>
+      <c r="J28" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>165</v>
+      </c>
+      <c r="B29" t="s">
+        <v>166</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" t="s">
+        <v>167</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" t="s">
+        <v>168</v>
+      </c>
+      <c r="H29" t="s">
+        <v>169</v>
+      </c>
+      <c r="I29" t="s">
+        <v>170</v>
+      </c>
+      <c r="J29" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B30" t="s">
+        <v>166</v>
+      </c>
+      <c r="C30" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" t="s">
+        <v>173</v>
+      </c>
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" t="s">
+        <v>168</v>
+      </c>
+      <c r="H30" t="s">
+        <v>174</v>
+      </c>
+      <c r="I30" t="s">
+        <v>175</v>
+      </c>
+      <c r="J30" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>177</v>
+      </c>
+      <c r="B31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" t="s">
+        <v>178</v>
+      </c>
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" t="s">
+        <v>168</v>
+      </c>
+      <c r="H31" t="s">
+        <v>179</v>
+      </c>
+      <c r="I31" t="s">
+        <v>180</v>
+      </c>
+      <c r="J31" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>182</v>
+      </c>
+      <c r="B32" t="s">
+        <v>166</v>
+      </c>
+      <c r="C32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" t="s">
+        <v>183</v>
+      </c>
+      <c r="F32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" t="s">
+        <v>168</v>
+      </c>
+      <c r="H32" t="s">
+        <v>184</v>
+      </c>
+      <c r="I32" t="s">
+        <v>185</v>
+      </c>
+      <c r="J32" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>187</v>
+      </c>
+      <c r="B33" t="s">
+        <v>166</v>
+      </c>
+      <c r="C33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" t="s">
+        <v>188</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" t="s">
+        <v>168</v>
+      </c>
+      <c r="H33" t="s">
+        <v>189</v>
+      </c>
+      <c r="I33" t="s">
+        <v>190</v>
+      </c>
+      <c r="J33" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>192</v>
+      </c>
+      <c r="B34" t="s">
+        <v>166</v>
+      </c>
+      <c r="C34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" t="s">
+        <v>193</v>
+      </c>
+      <c r="F34" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" t="s">
+        <v>168</v>
+      </c>
+      <c r="H34" t="s">
+        <v>194</v>
+      </c>
+      <c r="I34" t="s">
+        <v>195</v>
+      </c>
+      <c r="J34" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>197</v>
+      </c>
+      <c r="B35" t="s">
+        <v>198</v>
+      </c>
+      <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" t="s">
+        <v>199</v>
+      </c>
+      <c r="F35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" t="s">
+        <v>168</v>
+      </c>
+      <c r="H35" t="s">
+        <v>200</v>
+      </c>
+      <c r="I35" t="s">
+        <v>201</v>
+      </c>
+      <c r="J35" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>203</v>
+      </c>
+      <c r="B36" t="s">
+        <v>166</v>
+      </c>
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" t="s">
+        <v>204</v>
+      </c>
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" t="s">
+        <v>168</v>
+      </c>
+      <c r="H36" t="s">
+        <v>205</v>
+      </c>
+      <c r="I36" t="s">
+        <v>206</v>
+      </c>
+      <c r="J36" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>208</v>
+      </c>
+      <c r="B37" t="s">
+        <v>209</v>
+      </c>
+      <c r="C37" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" t="s">
+        <v>210</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" t="s">
+        <v>168</v>
+      </c>
+      <c r="H37" t="s">
+        <v>211</v>
+      </c>
+      <c r="I37" t="s">
+        <v>212</v>
+      </c>
+      <c r="J37" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>214</v>
+      </c>
+      <c r="B38" t="s">
+        <v>215</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" t="s">
+        <v>216</v>
+      </c>
+      <c r="F38" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" t="s">
+        <v>168</v>
+      </c>
+      <c r="H38" t="s">
+        <v>217</v>
+      </c>
+      <c r="I38" t="s">
+        <v>218</v>
+      </c>
+      <c r="J38" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>220</v>
+      </c>
+      <c r="B39" t="s">
+        <v>221</v>
+      </c>
+      <c r="C39" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" t="s">
+        <v>222</v>
+      </c>
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" t="s">
+        <v>168</v>
+      </c>
+      <c r="H39" t="s">
+        <v>223</v>
+      </c>
+      <c r="I39" t="s">
+        <v>224</v>
+      </c>
+      <c r="J39" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>226</v>
+      </c>
+      <c r="B40" t="s">
+        <v>166</v>
+      </c>
+      <c r="C40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" t="s">
+        <v>227</v>
+      </c>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" t="s">
+        <v>168</v>
+      </c>
+      <c r="H40" t="s">
+        <v>228</v>
+      </c>
+      <c r="I40" t="s">
+        <v>229</v>
+      </c>
+      <c r="J40" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>231</v>
+      </c>
+      <c r="B41" t="s">
+        <v>166</v>
+      </c>
+      <c r="C41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" t="s">
+        <v>232</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" t="s">
+        <v>168</v>
+      </c>
+      <c r="H41" t="s">
+        <v>233</v>
+      </c>
+      <c r="I41" t="s">
+        <v>234</v>
+      </c>
+      <c r="J41" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>236</v>
+      </c>
+      <c r="B42" t="s">
+        <v>237</v>
+      </c>
+      <c r="C42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" t="s">
+        <v>238</v>
+      </c>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" t="s">
+        <v>168</v>
+      </c>
+      <c r="H42" t="s">
+        <v>239</v>
+      </c>
+      <c r="I42" t="s">
+        <v>240</v>
+      </c>
+      <c r="J42" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>242</v>
+      </c>
+      <c r="B43" t="s">
+        <v>221</v>
+      </c>
+      <c r="C43" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
+        <v>243</v>
+      </c>
+      <c r="F43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" t="s">
+        <v>168</v>
+      </c>
+      <c r="H43" t="s">
+        <v>244</v>
+      </c>
+      <c r="I43" t="s">
+        <v>245</v>
+      </c>
+      <c r="J43" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>247</v>
+      </c>
+      <c r="B44" t="s">
+        <v>221</v>
+      </c>
+      <c r="C44" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" t="s">
+        <v>248</v>
+      </c>
+      <c r="F44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" t="s">
+        <v>168</v>
+      </c>
+      <c r="H44" t="s">
+        <v>249</v>
+      </c>
+      <c r="I44" t="s">
+        <v>250</v>
+      </c>
+      <c r="J44" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>252</v>
+      </c>
+      <c r="B45" t="s">
+        <v>166</v>
+      </c>
+      <c r="C45" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" t="s">
+        <v>253</v>
+      </c>
+      <c r="F45" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" t="s">
+        <v>168</v>
+      </c>
+      <c r="H45" t="s">
+        <v>254</v>
+      </c>
+      <c r="I45" t="s">
+        <v>255</v>
+      </c>
+      <c r="J45" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>257</v>
+      </c>
+      <c r="B46" t="s">
+        <v>166</v>
+      </c>
+      <c r="C46" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" t="s">
+        <v>258</v>
+      </c>
+      <c r="F46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" t="s">
+        <v>168</v>
+      </c>
+      <c r="H46" t="s">
+        <v>259</v>
+      </c>
+      <c r="I46" t="s">
+        <v>260</v>
+      </c>
+      <c r="J46" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>262</v>
+      </c>
+      <c r="B47" t="s">
+        <v>166</v>
+      </c>
+      <c r="C47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" t="s">
+        <v>263</v>
+      </c>
+      <c r="F47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47" t="s">
+        <v>168</v>
+      </c>
+      <c r="H47" t="s">
+        <v>264</v>
+      </c>
+      <c r="I47" t="s">
+        <v>265</v>
+      </c>
+      <c r="J47" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>267</v>
+      </c>
+      <c r="B48" t="s">
+        <v>166</v>
+      </c>
+      <c r="C48" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" t="s">
+        <v>268</v>
+      </c>
+      <c r="F48" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" t="s">
+        <v>168</v>
+      </c>
+      <c r="H48" t="s">
+        <v>269</v>
+      </c>
+      <c r="I48" t="s">
+        <v>270</v>
+      </c>
+      <c r="J48" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>272</v>
+      </c>
+      <c r="B49" t="s">
+        <v>273</v>
+      </c>
+      <c r="C49" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" t="s">
+        <v>274</v>
+      </c>
+      <c r="F49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" t="s">
+        <v>275</v>
+      </c>
+      <c r="H49" t="s">
+        <v>276</v>
+      </c>
+      <c r="I49" t="s">
+        <v>277</v>
+      </c>
+      <c r="J49" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>279</v>
+      </c>
+      <c r="B50" t="s">
+        <v>280</v>
+      </c>
+      <c r="C50" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" t="s">
+        <v>281</v>
+      </c>
+      <c r="F50" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" t="s">
+        <v>282</v>
+      </c>
+      <c r="H50" t="s">
+        <v>283</v>
+      </c>
+      <c r="I50" t="s">
+        <v>284</v>
+      </c>
+      <c r="J50" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>286</v>
+      </c>
+      <c r="B51" t="s">
+        <v>287</v>
+      </c>
+      <c r="C51" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" t="s">
+        <v>288</v>
+      </c>
+      <c r="F51" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" t="s">
+        <v>168</v>
+      </c>
+      <c r="H51" t="s">
+        <v>289</v>
+      </c>
+      <c r="I51" t="s">
+        <v>290</v>
+      </c>
+      <c r="J51" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>292</v>
+      </c>
+      <c r="B52" t="s">
+        <v>293</v>
+      </c>
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" t="s">
+        <v>294</v>
+      </c>
+      <c r="F52" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" t="s">
+        <v>295</v>
+      </c>
+      <c r="H52" t="s">
+        <v>296</v>
+      </c>
+      <c r="I52" t="s">
+        <v>297</v>
+      </c>
+      <c r="J52" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>299</v>
+      </c>
+      <c r="B53" t="s">
+        <v>166</v>
+      </c>
+      <c r="C53" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" t="s">
+        <v>300</v>
+      </c>
+      <c r="F53" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" t="s">
+        <v>168</v>
+      </c>
+      <c r="H53" t="s">
+        <v>301</v>
+      </c>
+      <c r="I53" t="s">
+        <v>302</v>
+      </c>
+      <c r="J53" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>304</v>
+      </c>
+      <c r="B54" t="s">
+        <v>287</v>
+      </c>
+      <c r="C54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" t="s">
+        <v>305</v>
+      </c>
+      <c r="F54" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" t="s">
+        <v>168</v>
+      </c>
+      <c r="H54" t="s">
+        <v>306</v>
+      </c>
+      <c r="I54" t="s">
+        <v>307</v>
+      </c>
+      <c r="J54" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
